--- a/output/pdf_financials_xlsx/BLDP.xlsx
+++ b/output/pdf_financials_xlsx/BLDP.xlsx
@@ -5211,22 +5211,22 @@
         <v>18.857</v>
       </c>
       <c r="I85" s="3" t="n">
-        <v>4.253</v>
+        <v>18.378</v>
       </c>
       <c r="J85" s="3" t="n">
-        <v>3.862</v>
+        <v>15.791</v>
       </c>
       <c r="K85" s="3" t="n">
-        <v>1.688</v>
+        <v>25.54</v>
       </c>
       <c r="L85" s="3" t="n">
-        <v>1.764</v>
+        <v>22.621</v>
       </c>
       <c r="M85" s="3" t="n">
-        <v>8.895</v>
+        <v>29.567</v>
       </c>
       <c r="N85" s="3" t="n">
-        <v>1.805</v>
+        <v>14.998</v>
       </c>
       <c r="O85" s="3" t="n">
         <v>15.74</v>
@@ -13662,7 +13662,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>OtherNonCurrentLiabilities</t>
+          <t>CurrentLiabilities</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -14510,7 +14510,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>OtherNonCurrentLiabilities</t>
+          <t>CurrentLiabilities</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">

--- a/output/pdf_financials_xlsx/BLDP.xlsx
+++ b/output/pdf_financials_xlsx/BLDP.xlsx
@@ -8440,7 +8440,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -20646,7 +20646,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E139" s="5" t="n">

--- a/output/pdf_financials_xlsx/BLDP.xlsx
+++ b/output/pdf_financials_xlsx/BLDP.xlsx
@@ -1054,28 +1054,28 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>-0</v>
+        <v>0.965</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>-0</v>
+        <v>1.197</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>-0</v>
+        <v>1.909</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>-0</v>
+        <v>1.332</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>-0</v>
+        <v>1.055</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>-0</v>
+        <v>1.099</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>-0</v>
+        <v>1.463</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>-0</v>
+        <v>-1.048</v>
       </c>
       <c r="J13" s="3" t="n">
         <v>-0</v>
@@ -1087,10 +1087,10 @@
         <v>-0</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>-0</v>
+        <v>10.107</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>-0</v>
+        <v>3.381</v>
       </c>
       <c r="O13" s="3" t="n">
         <v>-0</v>
@@ -1984,28 +1984,28 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-35.436</v>
+        <v>-36.401</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-39.777</v>
+        <v>-40.974</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-43.659</v>
+        <v>-45.568</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-21.239</v>
+        <v>-22.571</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-29.331</v>
+        <v>-30.386</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-6.363</v>
+        <v>-7.462</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-21.306</v>
+        <v>-22.769</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-6.477</v>
+        <v>-5.429</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>-26.953</v>
@@ -2017,10 +2017,10 @@
         <v>-49.339</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-114.613</v>
+        <v>-124.72</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-160.329</v>
+        <v>-163.71</v>
       </c>
       <c r="O27" s="3" t="n">
         <v>-174.002</v>
@@ -2094,28 +2094,28 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-26.821</v>
+        <v>-27.786</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-33.871</v>
+        <v>-35.068</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-37.731</v>
+        <v>-39.64</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-15.508</v>
+        <v>-16.84</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-23.721</v>
+        <v>-24.776</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-1.988</v>
+        <v>-3.087</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-16.762</v>
+        <v>-18.225</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-1.413</v>
+        <v>-0.365</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>-21.938</v>
@@ -2127,10 +2127,10 @@
         <v>-41.781</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-104.861</v>
+        <v>-114.968</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-146.556</v>
+        <v>-149.937</v>
       </c>
       <c r="O29" s="3" t="n">
         <v>-160.475</v>
@@ -2149,28 +2149,28 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-264.7157520726411</v>
+        <v>-274.2400315831031</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-465.3249072674818</v>
+        <v>-481.7694738288226</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-512.0233410232054</v>
+        <v>-537.9291627086443</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-92.53535413807506</v>
+        <v>-100.4833223939376</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-231.5147374585204</v>
+        <v>-241.8114386101893</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-19.93182273912172</v>
+        <v>-30.95047122518548</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>-69.31028779358253</v>
+        <v>-75.35974197816738</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>-3.396634615384615</v>
+        <v>-0.8774038461538461</v>
       </c>
       <c r="J30" s="3" t="n">
         <v>-73.93003976545124</v>
@@ -2182,10 +2182,10 @@
         <v>-199.1088448341594</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>-748.3122814529365</v>
+        <v>-820.4381645614786</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>1101.262398557259</v>
+        <v>1126.668169522092</v>
       </c>
       <c r="O30" s="3" t="n">
         <v>735.0785580138336</v>
@@ -35856,7 +35856,11 @@
           <t>Additions to intangible assets 10</t>
         </is>
       </c>
-      <c r="D304" t="inlineStr"/>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E304" t="inlineStr">
         <is>
           <t>-</t>
@@ -37636,7 +37640,11 @@
           <t>Additions to intangible assets 11</t>
         </is>
       </c>
-      <c r="D323" t="inlineStr"/>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E323" t="inlineStr">
         <is>
           <t>-</t>
@@ -39992,7 +40000,11 @@
           <t>Additions to intangible assets</t>
         </is>
       </c>
-      <c r="D348" t="inlineStr"/>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E348" t="inlineStr">
         <is>
           <t>-</t>
@@ -50244,7 +50256,11 @@
           <t>Net finance loss</t>
         </is>
       </c>
-      <c r="D461" t="inlineStr"/>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E461" t="inlineStr">
         <is>
           <t>-</t>
@@ -52846,7 +52862,11 @@
           <t>Net finance expense</t>
         </is>
       </c>
-      <c r="D489" t="inlineStr"/>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E489" s="5" t="n">
         <v>-0.965</v>
       </c>

--- a/output/pdf_financials_xlsx/BLDP.xlsx
+++ b/output/pdf_financials_xlsx/BLDP.xlsx
@@ -1304,10 +1304,10 @@
         <v>0.02</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>-2.038</v>
+        <v>0.13</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>0.38</v>
+        <v>-0.216</v>
       </c>
       <c r="N17" s="3" t="n">
         <v>0.042</v>
@@ -1506,16 +1506,16 @@
         <v>-35.439</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>-36.156</v>
+        <v>-39.911</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>-43.724</v>
+        <v>-43.659</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>-21.7</v>
+        <v>-21.724</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>-29.428</v>
+        <v>-29.748</v>
       </c>
       <c r="G20" s="3" t="n">
         <v>-6.574</v>
@@ -1532,23 +1532,35 @@
       <c r="K20" s="3" t="n">
         <v>-39.05</v>
       </c>
-      <c r="L20" s="3" t="n">
-        <v>-1.908</v>
-      </c>
-      <c r="M20" s="3" t="n">
-        <v>0.164</v>
-      </c>
-      <c r="N20" s="3" t="n">
-        <v>-173.494</v>
-      </c>
-      <c r="O20" s="3" t="n">
-        <v>-177.716</v>
-      </c>
-      <c r="P20" s="3" t="n">
-        <v>-324.245</v>
-      </c>
-      <c r="Q20" s="3" t="n">
-        <v>-90.914</v>
+      <c r="L20" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M20" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N20" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O20" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P20" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q20" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="21">
@@ -1588,22 +1600,22 @@
         <v>0</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>0</v>
+        <v>-1.908</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>0</v>
+        <v>0.164</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>0</v>
+        <v>-13.123</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>0</v>
+        <v>-33.506</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>0</v>
+        <v>-0.715</v>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>0</v>
+        <v>-90.914</v>
       </c>
     </row>
     <row r="22">
@@ -2234,10 +2246,10 @@
         <v>-0.05124263387138099</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>-4.130606619509921</v>
+        <v>-0.2634832485457752</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>-0.3315505221920725</v>
+        <v>-0.1884602968249675</v>
       </c>
       <c r="N31" s="3" t="n">
         <v>-0.0261961341990532</v>
@@ -6134,52 +6146,52 @@
         </is>
       </c>
       <c r="B103" s="3" t="n">
-        <v>0</v>
+        <v>1.276</v>
       </c>
       <c r="C103" s="3" t="n">
-        <v>0</v>
+        <v>0.042</v>
       </c>
       <c r="D103" s="3" t="n">
-        <v>0</v>
+        <v>-0.151</v>
       </c>
       <c r="E103" s="3" t="n">
-        <v>0</v>
+        <v>0.192</v>
       </c>
       <c r="F103" s="3" t="n">
-        <v>0</v>
+        <v>-0.434</v>
       </c>
       <c r="G103" s="3" t="n">
-        <v>0</v>
+        <v>-0.166</v>
       </c>
       <c r="H103" s="3" t="n">
-        <v>0</v>
+        <v>-1.322</v>
       </c>
       <c r="I103" s="3" t="n">
-        <v>0</v>
+        <v>0.93</v>
       </c>
       <c r="J103" s="3" t="n">
-        <v>0</v>
+        <v>0.426</v>
       </c>
       <c r="K103" s="3" t="n">
-        <v>0</v>
+        <v>-0.8120000000000001</v>
       </c>
       <c r="L103" s="3" t="n">
-        <v>0</v>
+        <v>-1.026</v>
       </c>
       <c r="M103" s="3" t="n">
-        <v>0</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="N103" s="3" t="n">
-        <v>0</v>
+        <v>-1.668</v>
       </c>
       <c r="O103" s="3" t="n">
-        <v>0</v>
+        <v>0.076</v>
       </c>
       <c r="P103" s="3" t="n">
-        <v>0</v>
+        <v>2.689</v>
       </c>
       <c r="Q103" s="3" t="n">
-        <v>0</v>
+        <v>2.893</v>
       </c>
     </row>
     <row r="104">
@@ -6415,7 +6427,7 @@
         <v>0</v>
       </c>
       <c r="D108" s="3" t="n">
-        <v>0</v>
+        <v>11.815</v>
       </c>
       <c r="E108" s="3" t="n">
         <v>0</v>
@@ -6861,10 +6873,10 @@
         <v>0</v>
       </c>
       <c r="F116" s="3" t="n">
-        <v>0</v>
+        <v>-3.411</v>
       </c>
       <c r="G116" s="3" t="n">
-        <v>0</v>
+        <v>-1.604</v>
       </c>
       <c r="H116" s="3" t="n">
         <v>0</v>
@@ -25332,7 +25344,11 @@
           <t>Prepaid expenses and other current assets</t>
         </is>
       </c>
-      <c r="D189" t="inlineStr"/>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E189" s="5" t="n">
         <v>1.276</v>
       </c>
@@ -29968,7 +29984,11 @@
           <t>Deferred income tax recovery 7</t>
         </is>
       </c>
-      <c r="D241" t="inlineStr"/>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E241" t="inlineStr">
         <is>
           <t>-</t>
@@ -31564,7 +31584,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D258" t="inlineStr"/>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E258" t="inlineStr">
         <is>
           <t>-</t>
@@ -32972,7 +32996,11 @@
           <t>Deferred income tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D273" t="inlineStr"/>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E273" t="inlineStr">
         <is>
           <t>-</t>
@@ -34940,7 +34968,11 @@
           <t>Net proceeds on issuance of share capital from private placement 19</t>
         </is>
       </c>
-      <c r="D294" t="inlineStr"/>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E294" t="inlineStr">
         <is>
           <t>-</t>
@@ -36226,7 +36258,11 @@
           <t>Net proceeds on issuance of share capital from private placement 20</t>
         </is>
       </c>
-      <c r="D308" t="inlineStr"/>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E308" t="inlineStr">
         <is>
           <t>-</t>
@@ -39150,7 +39186,11 @@
           <t>Additions to and acquisition of intangible assets 12</t>
         </is>
       </c>
-      <c r="D339" t="inlineStr"/>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E339" t="inlineStr">
         <is>
           <t>-</t>
@@ -41898,7 +41938,11 @@
           <t>Impairment loss on goodwill 13</t>
         </is>
       </c>
-      <c r="D368" t="inlineStr"/>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>AssetImpairmentCharge</t>
+        </is>
+      </c>
       <c r="E368" t="inlineStr">
         <is>
           <t>-</t>
@@ -43018,7 +43062,11 @@
           <t>Impairment loss on goodwill 11</t>
         </is>
       </c>
-      <c r="D380" t="inlineStr"/>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>AssetImpairmentCharge</t>
+        </is>
+      </c>
       <c r="E380" t="inlineStr">
         <is>
           <t>-</t>
@@ -47252,7 +47300,11 @@
           <t>Net loss from continued operations</t>
         </is>
       </c>
-      <c r="D427" t="inlineStr"/>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E427" t="inlineStr">
         <is>
           <t>-</t>
@@ -47338,7 +47390,11 @@
           <t>Net loss from discontinued operations 27</t>
         </is>
       </c>
-      <c r="D428" t="inlineStr"/>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E428" t="inlineStr">
         <is>
           <t>-</t>
@@ -48840,7 +48896,11 @@
           <t>Net loss from discontinued operations 26</t>
         </is>
       </c>
-      <c r="D445" t="inlineStr"/>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E445" t="inlineStr">
         <is>
           <t>-</t>
@@ -49724,7 +49784,11 @@
           <t>Net loss from discontinued operations 7</t>
         </is>
       </c>
-      <c r="D455" t="inlineStr"/>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E455" t="inlineStr">
         <is>
           <t>-</t>
@@ -50734,7 +50798,11 @@
           <t>Income tax recovery 29</t>
         </is>
       </c>
-      <c r="D466" t="inlineStr"/>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E466" t="inlineStr">
         <is>
           <t>-</t>
@@ -50828,7 +50896,11 @@
           <t>Net income from discontinued operations 8</t>
         </is>
       </c>
-      <c r="D467" t="inlineStr"/>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E467" t="inlineStr">
         <is>
           <t>-</t>
@@ -51108,7 +51180,11 @@
           <t>Income tax recovery (expense) 27</t>
         </is>
       </c>
-      <c r="D470" t="inlineStr"/>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E470" t="inlineStr">
         <is>
           <t>-</t>
@@ -51204,7 +51280,7 @@
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>NetIncomeContinuousOperations</t>
+          <t>NetIncomeDiscontinuousOperations</t>
         </is>
       </c>
       <c r="E471" t="inlineStr">
@@ -55018,7 +55094,11 @@
           <t>Net loss from continuing operations</t>
         </is>
       </c>
-      <c r="D512" t="inlineStr"/>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E512" t="inlineStr">
         <is>
           <t>-</t>
